--- a/output/yearly_surface_area_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_23_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497655199849</v>
+        <v>10.84497629111357</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907270773985</v>
+        <v>37.7890717986923</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.497787143782138</v>
+        <v>5.638177065489432</v>
       </c>
       <c r="C2" t="n">
-        <v>8.755226026473055</v>
+        <v>6.777004402415733</v>
       </c>
       <c r="D2" t="n">
-        <v>23.78185638767473</v>
+        <v>20.88177366932965</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.22338081267854</v>
+        <v>19.3306122966197</v>
       </c>
       <c r="C3" t="n">
-        <v>26.82625601854409</v>
+        <v>26.42864819832414</v>
       </c>
       <c r="D3" t="n">
-        <v>60.74073046175016</v>
+        <v>84.55302102825655</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.89854549575986</v>
+        <v>40.36848385092459</v>
       </c>
       <c r="C4" t="n">
-        <v>49.77460860531329</v>
+        <v>65.00053375047708</v>
       </c>
       <c r="D4" t="n">
-        <v>92.52972112526189</v>
+        <v>111.5206487162122</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.38066573400307</v>
+        <v>49.72552122010096</v>
       </c>
       <c r="C5" t="n">
-        <v>82.1231954602457</v>
+        <v>118.6442100582271</v>
       </c>
       <c r="D5" t="n">
-        <v>72.25663103256525</v>
+        <v>79.00614649926207</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.13719230334986</v>
+        <v>44.35732477327939</v>
       </c>
       <c r="C6" t="n">
-        <v>87.22533827921637</v>
+        <v>134.1990206843135</v>
       </c>
       <c r="D6" t="n">
-        <v>48.46299367243955</v>
+        <v>51.52211951887262</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.3625112492411</v>
       </c>
       <c r="C7" t="n">
-        <v>74.91814905877834</v>
+        <v>120.1924261878243</v>
       </c>
       <c r="D7" t="n">
-        <v>40.66300816219864</v>
+        <v>40.3036885024443</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.85522542358599</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C8" t="n">
-        <v>50.48637569089222</v>
+        <v>84.36648896444964</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>47.7031209493525</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.719707786992049</v>
+        <v>7.649462654040526</v>
       </c>
       <c r="C21" t="n">
-        <v>96.49634733740062</v>
+        <v>92.74973468024137</v>
       </c>
       <c r="D21" t="n">
-        <v>8.684671260366056</v>
+        <v>7.649462654040526</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.195629835052372</v>
+        <v>7.617380437251001</v>
       </c>
       <c r="C2" t="n">
-        <v>6.904631603967817</v>
+        <v>11.3254415161912</v>
       </c>
       <c r="D2" t="n">
-        <v>23.71313404837746</v>
+        <v>33.57871672835365</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.41620427333842</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="C3" t="n">
-        <v>30.66488954214912</v>
+        <v>26.20284622634737</v>
       </c>
       <c r="D3" t="n">
-        <v>64.93770189740528</v>
+        <v>81.54396431474008</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.07722357793278</v>
+        <v>38.09671966329748</v>
       </c>
       <c r="C4" t="n">
-        <v>58.89995351628739</v>
+        <v>64.73251662721769</v>
       </c>
       <c r="D4" t="n">
-        <v>101.0169300284756</v>
+        <v>123.6962837442811</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.81049130201392</v>
+        <v>54.73243451175969</v>
       </c>
       <c r="C5" t="n">
-        <v>86.27107951068848</v>
+        <v>119.0369091399258</v>
       </c>
       <c r="D5" t="n">
-        <v>86.59014751456868</v>
+        <v>97.38937226128361</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.50324532831367</v>
+        <v>54.09822549481625</v>
       </c>
       <c r="C6" t="n">
-        <v>109.0819874188631</v>
+        <v>157.665736058925</v>
       </c>
       <c r="D6" t="n">
-        <v>59.2101857908294</v>
+        <v>61.54478183152831</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.12402867256714</v>
+        <v>40.18391528252619</v>
       </c>
       <c r="C7" t="n">
-        <v>100.6693913411722</v>
+        <v>154.3876804744449</v>
       </c>
       <c r="D7" t="n">
-        <v>44.73529763941441</v>
+        <v>45.21439051908685</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.20008090968387</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="C8" t="n">
-        <v>74.2692138262712</v>
+        <v>117.6624623539802</v>
       </c>
       <c r="D8" t="n">
-        <v>39.22082078466007</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.75937400146829</v>
+        <v>11.09374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>48.03593342109217</v>
+        <v>73.55155625446676</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>34.87658719336794</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.912002535229536</v>
+        <v>7.821383104215948</v>
       </c>
       <c r="C21" t="n">
-        <v>105.823033908695</v>
+        <v>100.7003074667803</v>
       </c>
       <c r="D21" t="n">
-        <v>9.89000316903692</v>
+        <v>8.799055992242941</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.850856464412496</v>
+        <v>7.933503198018475</v>
       </c>
       <c r="C2" t="n">
-        <v>7.023423076181681</v>
+        <v>12.7263954901514</v>
       </c>
       <c r="D2" t="n">
-        <v>19.87253702936394</v>
+        <v>34.9197840923548</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.01569226773472</v>
+        <v>21.26956401250715</v>
       </c>
       <c r="C3" t="n">
-        <v>28.83883881225006</v>
+        <v>34.01755795215198</v>
       </c>
       <c r="D3" t="n">
-        <v>67.53933331365931</v>
+        <v>86.68341354647212</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.57496966398591</v>
+        <v>36.15678619970578</v>
       </c>
       <c r="C4" t="n">
-        <v>66.69797553111979</v>
+        <v>64.80909294814894</v>
       </c>
       <c r="D4" t="n">
-        <v>107.3855273859246</v>
+        <v>132.6429505730823</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.93950116189775</v>
+        <v>55.2233083638831</v>
       </c>
       <c r="C5" t="n">
-        <v>95.81857593448871</v>
+        <v>117.6133749687679</v>
       </c>
       <c r="D5" t="n">
-        <v>100.4818775296611</v>
+        <v>112.3610247510475</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.45419900083034</v>
+        <v>61.66553679915066</v>
       </c>
       <c r="C6" t="n">
-        <v>122.3247822014483</v>
+        <v>169.5399745417902</v>
       </c>
       <c r="D6" t="n">
-        <v>69.75611962984863</v>
+        <v>73.90204018488291</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.74770050667112</v>
+        <v>49.76577287597506</v>
       </c>
       <c r="C7" t="n">
-        <v>126.1810871837298</v>
+        <v>185.7083774830309</v>
       </c>
       <c r="D7" t="n">
-        <v>50.60418541540184</v>
+        <v>50.18497914568845</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.7952820603647</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="C8" t="n">
-        <v>101.9741340401162</v>
+        <v>152.7108553955914</v>
       </c>
       <c r="D8" t="n">
-        <v>41.55738032076748</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.30624853046277</v>
+        <v>15.64218617176442</v>
       </c>
       <c r="C9" t="n">
-        <v>67.8937442348924</v>
+        <v>102.8390537675576</v>
       </c>
       <c r="D9" t="n">
-        <v>37.60780930658255</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>60.78490910844128</v>
       </c>
       <c r="D10" t="n">
-        <v>37.01188845010476</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.91549724863931</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.089764965512963</v>
+        <v>7.976954039020313</v>
       </c>
       <c r="C21" t="n">
-        <v>114.2679301378706</v>
+        <v>107.6888795267742</v>
       </c>
       <c r="D21" t="n">
-        <v>11.12342682758032</v>
+        <v>9.971192548775392</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.753262531064561</v>
+        <v>7.333655350723674</v>
       </c>
       <c r="C2" t="n">
-        <v>4.607341976030281</v>
+        <v>8.857327787714723</v>
       </c>
       <c r="D2" t="n">
-        <v>16.12716953766235</v>
+        <v>28.76717122984004</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.78912953223196</v>
+        <v>25.07383636646354</v>
       </c>
       <c r="C3" t="n">
-        <v>42.34277848416494</v>
+        <v>49.79915229791946</v>
       </c>
       <c r="D3" t="n">
-        <v>75.97745483166067</v>
+        <v>94.7239272442535</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.58175978245763</v>
+        <v>26.53369520267854</v>
       </c>
       <c r="C4" t="n">
-        <v>86.88859881665971</v>
+        <v>93.55073873767856</v>
       </c>
       <c r="D4" t="n">
-        <v>106.734628658009</v>
+        <v>126.9635401040145</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.11511082777092</v>
+        <v>34.72932503773092</v>
       </c>
       <c r="C5" t="n">
-        <v>73.09111658117504</v>
+        <v>101.2918193856647</v>
       </c>
       <c r="D5" t="n">
-        <v>69.65499961631122</v>
+        <v>74.34284490408973</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.26924521733767</v>
+        <v>30.87302005544945</v>
       </c>
       <c r="C6" t="n">
-        <v>83.07941772418209</v>
+        <v>122.2845305455742</v>
       </c>
       <c r="D6" t="n">
-        <v>33.32837106377072</v>
+        <v>33.04660947265189</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.73883941513712</v>
+        <v>20.78065365579224</v>
       </c>
       <c r="C7" t="n">
-        <v>71.68427212098935</v>
+        <v>107.3766916565864</v>
       </c>
       <c r="D7" t="n">
-        <v>29.22466566001905</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>49.98568436172635</v>
+        <v>75.77128781376882</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>46.37187106239383</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.72062817711293</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.225843029705771</v>
+        <v>4.476769531365456</v>
       </c>
       <c r="C2" t="n">
-        <v>1.871211124294421</v>
+        <v>3.792491381505428</v>
       </c>
       <c r="D2" t="n">
-        <v>11.65530874481813</v>
+        <v>20.34868466592364</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.22033775857456</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="C3" t="n">
-        <v>29.86967390170921</v>
+        <v>43.04963683122264</v>
       </c>
       <c r="D3" t="n">
-        <v>72.87513208624073</v>
+        <v>96.85431976246907</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.18307240354219</v>
+        <v>35.50588747179015</v>
       </c>
       <c r="C4" t="n">
-        <v>99.76618345326513</v>
+        <v>111.4057842348153</v>
       </c>
       <c r="D4" t="n">
-        <v>118.4508057604904</v>
+        <v>142.7127367755419</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.1830724035422</v>
+        <v>38.65631585471817</v>
       </c>
       <c r="C5" t="n">
-        <v>115.6744232528805</v>
+        <v>134.0085616296896</v>
       </c>
       <c r="D5" t="n">
-        <v>87.0810213666921</v>
+        <v>93.06968236259763</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.74347041621788</v>
+        <v>36.38749691020379</v>
       </c>
       <c r="C6" t="n">
-        <v>100.7096429970463</v>
+        <v>144.4631929322139</v>
       </c>
       <c r="D6" t="n">
-        <v>42.42524529132167</v>
+        <v>41.29819892684633</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>93.18356509629025</v>
+        <v>134.7448724078747</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>65.84090978531233</v>
+        <v>99.30378028456487</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>50.03280825153018</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.973533869714341</v>
+        <v>4.231332605303753</v>
       </c>
       <c r="C2" t="n">
-        <v>5.734388340505619</v>
+        <v>4.11843161931537</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30682936753952</v>
+        <v>16.19294663384689</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.86981277042945</v>
+        <v>20.50380080319464</v>
       </c>
       <c r="C3" t="n">
-        <v>17.30330328735003</v>
+        <v>28.24488145118073</v>
       </c>
       <c r="D3" t="n">
-        <v>65.75746123045137</v>
+        <v>91.00801218367933</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.18453717733195</v>
+        <v>41.5681795455142</v>
       </c>
       <c r="C4" t="n">
-        <v>86.22493736858885</v>
+        <v>109.3382235696715</v>
       </c>
       <c r="D4" t="n">
-        <v>127.116692745877</v>
+        <v>156.1774065392868</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.28249096357838</v>
+        <v>45.3076565509903</v>
       </c>
       <c r="C5" t="n">
-        <v>152.3917873917112</v>
+        <v>169.4741974456057</v>
       </c>
       <c r="D5" t="n">
-        <v>107.3786551519949</v>
+        <v>118.0797051282851</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57366912111219</v>
+        <v>43.67304662341937</v>
       </c>
       <c r="C6" t="n">
-        <v>141.5248220534032</v>
+        <v>175.6179745787822</v>
       </c>
       <c r="D6" t="n">
-        <v>57.23785465299754</v>
+        <v>56.75483478250812</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.66194429903638</v>
+        <v>28.38625312059227</v>
       </c>
       <c r="C7" t="n">
-        <v>120.1325395778652</v>
+        <v>169.7785392339221</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>134.8528646553419</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>60.79374483777947</v>
+        <v>80.20780568926014</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>40.42837046088366</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.886338250485622</v>
+        <v>2.559416264971435</v>
       </c>
       <c r="C2" t="n">
-        <v>2.553525778745954</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="D2" t="n">
-        <v>11.26162791541516</v>
+        <v>11.29500733735955</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.5311098124643</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="C3" t="n">
-        <v>20.78359889890498</v>
+        <v>24.91675673378405</v>
       </c>
       <c r="D3" t="n">
-        <v>65.94399329425825</v>
+        <v>87.92041565382311</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.31515067972578</v>
+        <v>45.43528375254238</v>
       </c>
       <c r="C4" t="n">
-        <v>78.0567964692554</v>
+        <v>107.2323747440621</v>
       </c>
       <c r="D4" t="n">
-        <v>133.5618664242573</v>
+        <v>166.4641589843849</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.61414176116455</v>
+        <v>47.07480241863456</v>
       </c>
       <c r="C5" t="n">
-        <v>176.9109363052752</v>
+        <v>203.8844544794564</v>
       </c>
       <c r="D5" t="n">
-        <v>115.8707727937298</v>
+        <v>124.5837836689203</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.26674194258143</v>
+        <v>34.97868895460962</v>
       </c>
       <c r="C6" t="n">
-        <v>177.4292990931176</v>
+        <v>208.7450873631823</v>
       </c>
       <c r="D6" t="n">
-        <v>56.23156325614456</v>
+        <v>55.2252718592916</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>126.0613139638117</v>
+        <v>176.1864064995411</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>76.10508203321274</v>
+        <v>98.71964040053801</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>33.28124717396686</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.858268477689965</v>
+        <v>3.204424506661589</v>
       </c>
       <c r="C2" t="n">
-        <v>4.106650646864408</v>
+        <v>4.357978059151591</v>
       </c>
       <c r="D2" t="n">
-        <v>12.36314883958008</v>
+        <v>18.45587509213579</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.28719441345458</v>
+        <v>14.71639808665969</v>
       </c>
       <c r="C3" t="n">
-        <v>14.98637870532756</v>
+        <v>16.34119053718816</v>
       </c>
       <c r="D3" t="n">
-        <v>60.65237316836794</v>
+        <v>78.5790862479147</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.5073522455799</v>
+        <v>42.07868835172254</v>
       </c>
       <c r="C4" t="n">
-        <v>65.19197455280519</v>
+        <v>86.46742905153782</v>
       </c>
       <c r="D4" t="n">
-        <v>135.6804779700219</v>
+        <v>170.9438737588631</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.2849785428014</v>
+        <v>56.05779391249288</v>
       </c>
       <c r="C5" t="n">
-        <v>162.307439204604</v>
+        <v>200.6446870554419</v>
       </c>
       <c r="D5" t="n">
-        <v>133.9840179370835</v>
+        <v>148.9311267342412</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.249152599363</v>
+        <v>46.00764266411829</v>
       </c>
       <c r="C6" t="n">
-        <v>227.2205974094031</v>
+        <v>262.8030612021245</v>
       </c>
       <c r="D6" t="n">
-        <v>74.74732495823942</v>
+        <v>75.06933820523237</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.67895280517807</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>186.5467900224577</v>
+        <v>229.1860563133051</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>115.5762484824558</v>
+        <v>152.3770611761474</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>55.80155776168444</v>
+        <v>64.89843198923538</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.565887588273662</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.21334235145782</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.700787934382975</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C2" t="n">
-        <v>2.638937829015426</v>
+        <v>3.049308369390593</v>
       </c>
       <c r="D2" t="n">
-        <v>9.434595437811847</v>
+        <v>14.81260936167588</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.14345833800705</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="C3" t="n">
-        <v>15.79632056133118</v>
+        <v>16.74861583445059</v>
       </c>
       <c r="D3" t="n">
-        <v>57.402788267311</v>
+        <v>75.96272861609695</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.2618742617892</v>
+        <v>37.76488893926206</v>
       </c>
       <c r="C4" t="n">
-        <v>54.38195058134357</v>
+        <v>69.8376046893011</v>
       </c>
       <c r="D4" t="n">
-        <v>137.3268688700438</v>
+        <v>171.5437216061579</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.03449400949822</v>
+        <v>60.05841580729864</v>
       </c>
       <c r="C5" t="n">
-        <v>150.9682532205533</v>
+        <v>190.3608798534566</v>
       </c>
       <c r="D5" t="n">
-        <v>145.8140777732575</v>
+        <v>166.2344300215912</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.2655235151657</v>
+        <v>53.73596059194917</v>
       </c>
       <c r="C6" t="n">
-        <v>249.3992597960427</v>
+        <v>293.6358296016998</v>
       </c>
       <c r="D6" t="n">
-        <v>89.92219922278237</v>
+        <v>88.63414623481054</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>239.3068933963855</v>
+        <v>282.8444588366188</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>44.79518424937346</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>151.9598184018425</v>
+        <v>193.0999559483051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>68.89218165011141</v>
+        <v>73.1078062921472</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.265112937875643</v>
+        <v>3.048326621686346</v>
       </c>
       <c r="C2" t="n">
-        <v>8.732645829275379</v>
+        <v>10.15323475732051</v>
       </c>
       <c r="D2" t="n">
-        <v>11.57676892847839</v>
+        <v>21.72018620875643</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.20803270230909</v>
+        <v>10.7108674533327</v>
       </c>
       <c r="C3" t="n">
-        <v>12.99833960422777</v>
+        <v>14.40714755982194</v>
       </c>
       <c r="D3" t="n">
-        <v>52.327152636355</v>
+        <v>71.59886007071988</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.23787034853076</v>
+        <v>31.83022406709009</v>
       </c>
       <c r="C4" t="n">
-        <v>47.23482729442679</v>
+        <v>57.52157973952487</v>
       </c>
       <c r="D4" t="n">
-        <v>134.9785283614855</v>
+        <v>168.1616007650277</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.96086293167971</v>
+        <v>59.24847395129502</v>
       </c>
       <c r="C5" t="n">
-        <v>127.7744637077224</v>
+        <v>164.3200219983099</v>
       </c>
       <c r="D5" t="n">
-        <v>158.4049920802229</v>
+        <v>183.1695779198487</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.74353683614267</v>
+        <v>63.51711296936016</v>
       </c>
       <c r="C6" t="n">
-        <v>246.3803856054838</v>
+        <v>298.1440150596011</v>
       </c>
       <c r="D6" t="n">
-        <v>108.8002258277443</v>
+        <v>110.4505437185832</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.4890178343687</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="C7" t="n">
-        <v>294.4624611686755</v>
+        <v>338.5390060985403</v>
       </c>
       <c r="D7" t="n">
-        <v>58.50921792999716</v>
+        <v>54.5567016726995</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>219.4696992843744</v>
+        <v>263.8643304704152</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>116.484365108884</v>
+        <v>131.3499888465892</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.565527735375168</v>
+        <v>6.346017160251383</v>
       </c>
       <c r="C2" t="n">
-        <v>3.53036474447153</v>
+        <v>10.7275571643049</v>
       </c>
       <c r="D2" t="n">
-        <v>13.10044136546944</v>
+        <v>15.70010928631499</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.681553890925539</v>
+        <v>2.205987091442583</v>
       </c>
       <c r="C2" t="n">
-        <v>4.821362975556085</v>
+        <v>5.929756133650734</v>
       </c>
       <c r="D2" t="n">
-        <v>8.427322293254619</v>
+        <v>16.16054895960675</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18058482431918</v>
+        <v>14.41205629834318</v>
       </c>
       <c r="C3" t="n">
-        <v>21.68189804829081</v>
+        <v>23.54721868635975</v>
       </c>
       <c r="D3" t="n">
-        <v>57.3880620517473</v>
+        <v>79.15831739342032</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.70254011227577</v>
+        <v>44.43979158043612</v>
       </c>
       <c r="C4" t="n">
-        <v>68.68895987533233</v>
+        <v>86.33980184998573</v>
       </c>
       <c r="D4" t="n">
-        <v>140.7728033119502</v>
+        <v>172.9859089836965</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.11068511533519</v>
+        <v>36.86462629446773</v>
       </c>
       <c r="C5" t="n">
-        <v>200.6937744406543</v>
+        <v>248.4067128670492</v>
       </c>
       <c r="D5" t="n">
-        <v>147.4094177926586</v>
+        <v>165.5226629360123</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.26545709524092</v>
+        <v>19.68305972244431</v>
       </c>
       <c r="C6" t="n">
-        <v>247.0646637553439</v>
+        <v>278.501206993031</v>
       </c>
       <c r="D6" t="n">
-        <v>87.50709987033521</v>
+        <v>84.28696740040567</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.545712854840985</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>154.3277938644858</v>
+        <v>185.5287176531537</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>85.86856295194725</v>
+        <v>96.80032363873549</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.48831382410494</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.216426463290803</v>
+        <v>6.65134069627214</v>
       </c>
       <c r="C2" t="n">
-        <v>4.495422737746145</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="D2" t="n">
-        <v>15.88369610700915</v>
+        <v>21.98623983660732</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.82515109765283</v>
+        <v>13.47939597930871</v>
       </c>
       <c r="C3" t="n">
-        <v>8.894634200476103</v>
+        <v>27.03242303643592</v>
       </c>
       <c r="D3" t="n">
-        <v>14.1420756796753</v>
+        <v>16.32155558310322</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39819142265092</v>
+        <v>13.39637897872792</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14347274211362</v>
+        <v>70.13398406510501</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576257814429519</v>
+        <v>1.576044585732697</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.39863062565321</v>
+        <v>6.105488972710914</v>
       </c>
       <c r="C2" t="n">
-        <v>4.095851422117692</v>
+        <v>4.417864669110647</v>
       </c>
       <c r="D2" t="n">
-        <v>17.30821202587127</v>
+        <v>23.6846633649543</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.61746255270901</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="C3" t="n">
-        <v>14.47586989911922</v>
+        <v>24.47987900539422</v>
       </c>
       <c r="D3" t="n">
-        <v>24.06754496961056</v>
+        <v>30.84651286743478</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.78373776762522</v>
+        <v>15.65985763044087</v>
       </c>
       <c r="C4" t="n">
-        <v>14.11556849166064</v>
+        <v>41.73409490753191</v>
       </c>
       <c r="D4" t="n">
-        <v>22.47515019332223</v>
+        <v>23.623795007291</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44273679106122</v>
+        <v>15.43515953387987</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15421578170998</v>
+        <v>86.11194266269824</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251102482328678</v>
+        <v>3.2495072702905</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.511130701014094</v>
+        <v>4.816454237034852</v>
       </c>
       <c r="C2" t="n">
-        <v>4.651520622721387</v>
+        <v>7.460300804571512</v>
       </c>
       <c r="D2" t="n">
-        <v>26.03496736892117</v>
+        <v>22.26603793231766</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2359636063845</v>
+        <v>20.469439633546</v>
       </c>
       <c r="C3" t="n">
-        <v>15.35944283294135</v>
+        <v>20.11601046001715</v>
       </c>
       <c r="D3" t="n">
-        <v>32.32895190084746</v>
+        <v>42.63730279543898</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.21913502669207</v>
+        <v>27.47813649416398</v>
       </c>
       <c r="C4" t="n">
-        <v>27.00591584842126</v>
+        <v>53.06739040535709</v>
       </c>
       <c r="D4" t="n">
-        <v>29.48188355853172</v>
+        <v>33.75739481052658</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.37002107350981</v>
+        <v>13.59720570381833</v>
       </c>
       <c r="C5" t="n">
-        <v>17.40147805777472</v>
+        <v>45.52854978444584</v>
       </c>
       <c r="D5" t="n">
-        <v>30.50780990946964</v>
+        <v>31.14594591723007</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.82722207071512</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74058346144476</v>
+        <v>16.72184268601755</v>
       </c>
       <c r="C21" t="n">
-        <v>102.117559114813</v>
+        <v>102.0032403847071</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022175038433428</v>
+        <v>4.180460671504388</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.612250714551515</v>
+        <v>7.345436323174635</v>
       </c>
       <c r="C2" t="n">
-        <v>5.430046552189108</v>
+        <v>11.00342826919825</v>
       </c>
       <c r="D2" t="n">
-        <v>28.41865079483242</v>
+        <v>34.43578247416112</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.71425466480195</v>
+        <v>18.27523351455438</v>
       </c>
       <c r="C3" t="n">
-        <v>16.94496537529995</v>
+        <v>25.09838005906971</v>
       </c>
       <c r="D3" t="n">
-        <v>44.92477494633405</v>
+        <v>50.07404165510857</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.57947749187965</v>
+        <v>33.73186937021616</v>
       </c>
       <c r="C4" t="n">
-        <v>33.51490312757761</v>
+        <v>51.03811790067893</v>
       </c>
       <c r="D4" t="n">
-        <v>38.24987230515998</v>
+        <v>46.78813208899449</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.40272184738622</v>
+        <v>27.41530464109218</v>
       </c>
       <c r="C5" t="n">
-        <v>35.26928627506667</v>
+        <v>73.87651474457249</v>
       </c>
       <c r="D5" t="n">
-        <v>34.3366259560322</v>
+        <v>35.7356164345839</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.35096695650162</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>20.24658290468198</v>
+        <v>43.31078172055229</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.40016181936776</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0732306740386</v>
+        <v>18.03821061817965</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9063143972994</v>
+        <v>117.6778502233625</v>
       </c>
       <c r="D21" t="n">
-        <v>6.88504025677661</v>
+        <v>6.012736872726548</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.102142818970673</v>
+        <v>7.473063524726721</v>
       </c>
       <c r="C2" t="n">
-        <v>6.763259934556276</v>
+        <v>6.937029278207961</v>
       </c>
       <c r="D2" t="n">
-        <v>24.25211353800896</v>
+        <v>37.29365004122359</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.47586989911922</v>
+        <v>19.56623174563893</v>
       </c>
       <c r="C3" t="n">
-        <v>18.2212373908208</v>
+        <v>32.86400439966197</v>
       </c>
       <c r="D3" t="n">
-        <v>53.18127313904972</v>
+        <v>61.2512392679585</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.96013355922015</v>
+        <v>24.91282974296706</v>
       </c>
       <c r="C4" t="n">
-        <v>32.32797015314322</v>
+        <v>48.05164138436013</v>
       </c>
       <c r="D4" t="n">
-        <v>44.54189334167778</v>
+        <v>52.83766144256334</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.21204180858409</v>
+        <v>23.90555659840983</v>
       </c>
       <c r="C5" t="n">
-        <v>36.81553890925539</v>
+        <v>62.29189183446013</v>
       </c>
       <c r="D5" t="n">
-        <v>32.79037332184348</v>
+        <v>35.63744166415923</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.59876828859932</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>26.64659618866693</v>
+        <v>55.06426523579511</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>31.47679489356124</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>16.28915790886308</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.77592484372025</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.067268822571643</v>
+        <v>7.044935731043515</v>
       </c>
       <c r="C21" t="n">
-        <v>67.13905381443061</v>
+        <v>66.04627247853296</v>
       </c>
       <c r="D21" t="n">
-        <v>5.300451616928732</v>
+        <v>4.403084831902197</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.539601384437251</v>
+        <v>5.62639609303847</v>
       </c>
       <c r="C2" t="n">
-        <v>4.201880174176349</v>
+        <v>5.325981295538947</v>
       </c>
       <c r="D2" t="n">
-        <v>20.09146676741097</v>
+        <v>29.1019471969882</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.68971097219578</v>
+        <v>23.40977400776519</v>
       </c>
       <c r="C3" t="n">
-        <v>23.70429831903924</v>
+        <v>29.1922679857789</v>
       </c>
       <c r="D3" t="n">
-        <v>61.16288197457629</v>
+        <v>77.77896186895356</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.69961056469625</v>
+        <v>32.71085175779947</v>
       </c>
       <c r="C4" t="n">
-        <v>41.04490801915065</v>
+        <v>69.30157044278235</v>
       </c>
       <c r="D4" t="n">
-        <v>62.97126124579891</v>
+        <v>72.68369128391261</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.59969328304134</v>
+        <v>31.88225669541517</v>
       </c>
       <c r="C5" t="n">
-        <v>51.36994862471437</v>
+        <v>78.3189231062893</v>
       </c>
       <c r="D5" t="n">
-        <v>42.11697651218817</v>
+        <v>46.8784528777852</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.06419881587032</v>
+        <v>23.82898027747859</v>
       </c>
       <c r="C6" t="n">
-        <v>46.0478943199924</v>
+        <v>80.62406671586082</v>
       </c>
       <c r="D6" t="n">
-        <v>35.30070220160257</v>
+        <v>36.18623863083319</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>29.76364514965055</v>
+        <v>56.95216607106171</v>
       </c>
       <c r="D7" t="n">
         <v>33.83593462686632</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>20.9455872701057</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.62968549351647</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>34.82848155585983</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6308,10 +6308,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295435930020039</v>
+        <v>7.260637701015464</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51400675646292</v>
+        <v>75.32911614803545</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383506438767534</v>
+        <v>5.445478275761599</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.732023934469626</v>
+        <v>5.245477983790708</v>
       </c>
       <c r="C2" t="n">
-        <v>8.304603830223769</v>
+        <v>7.347399818583129</v>
       </c>
       <c r="D2" t="n">
-        <v>15.19843620944487</v>
+        <v>27.13452479767759</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.22828955119978</v>
+        <v>21.17138924208247</v>
       </c>
       <c r="C3" t="n">
-        <v>19.12444527872787</v>
+        <v>24.19026343264141</v>
       </c>
       <c r="D3" t="n">
-        <v>63.25891332314323</v>
+        <v>82.59443435828416</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.45185029032756</v>
+        <v>39.93455136564751</v>
       </c>
       <c r="C4" t="n">
-        <v>52.23781359526853</v>
+        <v>71.45847014901258</v>
       </c>
       <c r="D4" t="n">
-        <v>80.41789969796898</v>
+        <v>93.39758609581605</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.63744166415923</v>
+        <v>40.84070449666732</v>
       </c>
       <c r="C5" t="n">
-        <v>65.89981464756715</v>
+        <v>104.9488295839841</v>
       </c>
       <c r="D5" t="n">
-        <v>55.98416283467437</v>
+        <v>62.39006660488482</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.00635781677777</v>
+        <v>34.25415914887547</v>
       </c>
       <c r="C6" t="n">
-        <v>66.37498053642261</v>
+        <v>104.4932986492135</v>
       </c>
       <c r="D6" t="n">
-        <v>40.6139207769863</v>
+        <v>42.34474197957343</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>50.30475236560656</v>
+        <v>88.99150239915636</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>52.90638378186061</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.513499896957809</v>
+        <v>7.462521057157896</v>
       </c>
       <c r="C21" t="n">
-        <v>87.34443630213453</v>
+        <v>83.95336189302633</v>
       </c>
       <c r="D21" t="n">
-        <v>7.513499896957809</v>
+        <v>6.529705925013158</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_23_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497629111357</v>
+        <v>10.84497633542676</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890717986923</v>
+        <v>37.78907195310061</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.638177065489432</v>
+        <v>5.352488483553611</v>
       </c>
       <c r="C2" t="n">
-        <v>6.777004402415733</v>
+        <v>13.90351098754333</v>
       </c>
       <c r="D2" t="n">
-        <v>20.88177366932965</v>
+        <v>28.36956340962008</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3306122966197</v>
+        <v>16.8369731278328</v>
       </c>
       <c r="C3" t="n">
-        <v>26.42864819832414</v>
+        <v>31.76444697090555</v>
       </c>
       <c r="D3" t="n">
-        <v>84.55302102825655</v>
+        <v>78.07839491874883</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.36848385092459</v>
+        <v>35.21234490822035</v>
       </c>
       <c r="C4" t="n">
-        <v>65.00053375047708</v>
+        <v>71.89240263428968</v>
       </c>
       <c r="D4" t="n">
-        <v>111.5206487162122</v>
+        <v>97.11153766098174</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.72552122010096</v>
+        <v>44.05592822807562</v>
       </c>
       <c r="C5" t="n">
-        <v>118.6442100582271</v>
+        <v>122.4484824121835</v>
       </c>
       <c r="D5" t="n">
-        <v>79.00614649926207</v>
+        <v>72.64933011426398</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.35732477327939</v>
+        <v>41.861722109084</v>
       </c>
       <c r="C6" t="n">
-        <v>134.1990206843135</v>
+        <v>156.2166764474567</v>
       </c>
       <c r="D6" t="n">
-        <v>51.52211951887262</v>
+        <v>49.79129831628549</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.3625112492411</v>
+        <v>29.10489244010094</v>
       </c>
       <c r="C7" t="n">
-        <v>120.1924261878243</v>
+        <v>140.3742137440259</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>39.94436884268997</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C8" t="n">
-        <v>84.36648896444964</v>
+        <v>84.19959185472769</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -881,7 +881,7 @@
         <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>47.7031209493525</v>
+        <v>43.15468383557703</v>
       </c>
       <c r="D9" t="n">
         <v>33.39218466454675</v>
@@ -895,10 +895,10 @@
         <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -968,7 +968,7 @@
         <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.649462654040526</v>
+        <v>7.651707142888808</v>
       </c>
       <c r="C21" t="n">
-        <v>92.74973468024137</v>
+        <v>92.7769491075268</v>
       </c>
       <c r="D21" t="n">
-        <v>7.649462654040526</v>
+        <v>7.651707142888808</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.617380437251001</v>
+        <v>5.939573610693203</v>
       </c>
       <c r="C2" t="n">
-        <v>11.3254415161912</v>
+        <v>17.50456156672063</v>
       </c>
       <c r="D2" t="n">
-        <v>33.57871672835365</v>
+        <v>35.61682496237003</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.8986433067511</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="C3" t="n">
-        <v>26.20284622634737</v>
+        <v>42.54894550205677</v>
       </c>
       <c r="D3" t="n">
-        <v>81.54396431474008</v>
+        <v>81.11690406339271</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.09671966329748</v>
+        <v>33.51490312757761</v>
       </c>
       <c r="C4" t="n">
-        <v>64.73251662721769</v>
+        <v>75.31281163588557</v>
       </c>
       <c r="D4" t="n">
-        <v>123.6962837442811</v>
+        <v>109.491376211534</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.73243451175969</v>
+        <v>47.56567627075797</v>
       </c>
       <c r="C5" t="n">
-        <v>119.0369091399258</v>
+        <v>125.6882498361979</v>
       </c>
       <c r="D5" t="n">
-        <v>97.38937226128361</v>
+        <v>87.96459430051422</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.09822549481625</v>
+        <v>49.42903341341842</v>
       </c>
       <c r="C6" t="n">
-        <v>157.665736058925</v>
+        <v>174.0079083438175</v>
       </c>
       <c r="D6" t="n">
-        <v>61.54478183152831</v>
+        <v>58.6064109527176</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.18391528252619</v>
+        <v>38.14777054391831</v>
       </c>
       <c r="C7" t="n">
-        <v>154.3876804744449</v>
+        <v>177.6835717485175</v>
       </c>
       <c r="D7" t="n">
-        <v>45.21439051908685</v>
+        <v>44.49575119957818</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.94835258676919</v>
+        <v>22.44766125760332</v>
       </c>
       <c r="C8" t="n">
-        <v>117.6624623539802</v>
+        <v>130.0128484734051</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>73.55155625446676</v>
+        <v>69.66874408417063</v>
       </c>
       <c r="D9" t="n">
         <v>34.94530953266521</v>
@@ -1206,10 +1206,10 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>42.56367171762047</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -1293,7 +1293,7 @@
         <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.821383104215948</v>
+        <v>7.82184300934863</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7003074667803</v>
+        <v>100.7062287453636</v>
       </c>
       <c r="D21" t="n">
-        <v>8.799055992242941</v>
+        <v>8.799573385517208</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.933503198018475</v>
+        <v>7.701810739816227</v>
       </c>
       <c r="C2" t="n">
-        <v>12.7263954901514</v>
+        <v>11.32249627307846</v>
       </c>
       <c r="D2" t="n">
-        <v>34.9197840923548</v>
+        <v>30.80626121156066</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.26956401250715</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C3" t="n">
-        <v>34.01755795215198</v>
+        <v>53.38744015694155</v>
       </c>
       <c r="D3" t="n">
-        <v>86.68341354647212</v>
+        <v>87.55716900325179</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.15678619970578</v>
+        <v>32.25139383221197</v>
       </c>
       <c r="C4" t="n">
-        <v>64.80909294814894</v>
+        <v>87.59054842519618</v>
       </c>
       <c r="D4" t="n">
-        <v>132.6429505730823</v>
+        <v>120.7608581085832</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.2233083638831</v>
+        <v>48.64559874542947</v>
       </c>
       <c r="C5" t="n">
-        <v>117.6133749687679</v>
+        <v>130.7687942056752</v>
       </c>
       <c r="D5" t="n">
-        <v>112.3610247510475</v>
+        <v>100.899120303966</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.66553679915066</v>
+        <v>54.82275530055039</v>
       </c>
       <c r="C6" t="n">
-        <v>169.5399745417902</v>
+        <v>183.1450342272425</v>
       </c>
       <c r="D6" t="n">
-        <v>73.90204018488291</v>
+        <v>69.35360307110744</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.76577287597506</v>
+        <v>46.05280305851362</v>
       </c>
       <c r="C7" t="n">
-        <v>185.7083774830309</v>
+        <v>206.8483507985775</v>
       </c>
       <c r="D7" t="n">
-        <v>50.18497914568845</v>
+        <v>48.98724694650735</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.37665662772806</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="C8" t="n">
-        <v>152.7108553955914</v>
+        <v>173.739891220558</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.64218617176442</v>
+        <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>102.8390537675576</v>
+        <v>105.2796785603152</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>60.78490910844128</v>
+        <v>56.22959976073607</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1548,7 +1548,7 @@
         <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1604,7 +1604,7 @@
         <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.976954039020313</v>
+        <v>7.974561715896357</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6888795267742</v>
+        <v>107.6565831646008</v>
       </c>
       <c r="D21" t="n">
-        <v>9.971192548775392</v>
+        <v>9.968202144870446</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.333655350723674</v>
+        <v>7.023423076181681</v>
       </c>
       <c r="C2" t="n">
-        <v>8.857327787714723</v>
+        <v>7.970809610779853</v>
       </c>
       <c r="D2" t="n">
-        <v>28.76717122984004</v>
+        <v>25.48518865454295</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.07383636646354</v>
+        <v>21.55427084673872</v>
       </c>
       <c r="C3" t="n">
-        <v>49.79915229791946</v>
+        <v>71.23561342014857</v>
       </c>
       <c r="D3" t="n">
-        <v>94.7239272442535</v>
+        <v>94.12015240614171</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.53369520267854</v>
+        <v>23.36854060418683</v>
       </c>
       <c r="C4" t="n">
-        <v>93.55073873767856</v>
+        <v>111.5206487162122</v>
       </c>
       <c r="D4" t="n">
-        <v>126.9635401040145</v>
+        <v>115.5919564457237</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.72932503773092</v>
+        <v>30.87596529856219</v>
       </c>
       <c r="C5" t="n">
-        <v>101.2918193856647</v>
+        <v>109.4403253309132</v>
       </c>
       <c r="D5" t="n">
-        <v>74.34284490408973</v>
+        <v>67.59332943739291</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.87302005544945</v>
+        <v>28.57867567062465</v>
       </c>
       <c r="C6" t="n">
-        <v>122.2845305455742</v>
+        <v>136.2116034780195</v>
       </c>
       <c r="D6" t="n">
-        <v>33.04660947265189</v>
+        <v>32.24157635516951</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.78065365579224</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>107.3766916565864</v>
+        <v>122.1686843164731</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>75.77128781376882</v>
+        <v>77.60715602071035</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>46.37187106239383</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
         <v>27.17968519207294</v>
@@ -1828,7 +1828,7 @@
         <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1845,7 +1845,7 @@
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>27.72062817711293</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1901,7 +1901,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.476769531365456</v>
+        <v>4.367795536194059</v>
       </c>
       <c r="C2" t="n">
-        <v>3.792491381505428</v>
+        <v>4.34619708670063</v>
       </c>
       <c r="D2" t="n">
-        <v>20.34868466592364</v>
+        <v>18.15055155611503</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.75124228239384</v>
+        <v>23.15942834318226</v>
       </c>
       <c r="C3" t="n">
-        <v>43.04963683122264</v>
+        <v>52.54804586981053</v>
       </c>
       <c r="D3" t="n">
-        <v>96.85431976246907</v>
+        <v>93.1089522707675</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.50588747179015</v>
+        <v>30.60500293219007</v>
       </c>
       <c r="C4" t="n">
-        <v>111.4057842348153</v>
+        <v>144.9462128027033</v>
       </c>
       <c r="D4" t="n">
-        <v>142.7127367755419</v>
+        <v>132.8854422560313</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.65631585471817</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>134.0085616296896</v>
+        <v>153.7416904850505</v>
       </c>
       <c r="D5" t="n">
-        <v>93.06968236259763</v>
+        <v>84.65119579868124</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>33.56988099901544</v>
       </c>
       <c r="C6" t="n">
-        <v>144.4631929322139</v>
+        <v>158.672027455778</v>
       </c>
       <c r="D6" t="n">
-        <v>41.29819892684633</v>
+        <v>39.56737772425921</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>134.7448724078747</v>
+        <v>151.3933499764921</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>99.30378028456487</v>
+        <v>102.3913768144211</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -2125,7 +2125,7 @@
         <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>50.03280825153018</v>
+        <v>46.92655851529327</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2139,10 +2139,10 @@
         <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2198,7 +2198,7 @@
         <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.231332605303753</v>
+        <v>3.889684404225862</v>
       </c>
       <c r="C2" t="n">
-        <v>4.11843161931537</v>
+        <v>11.80257090045516</v>
       </c>
       <c r="D2" t="n">
-        <v>16.19294663384689</v>
+        <v>16.82421040767759</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.50380080319464</v>
+        <v>19.19807635654638</v>
       </c>
       <c r="C3" t="n">
-        <v>28.24488145118073</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D3" t="n">
-        <v>91.00801218367933</v>
+        <v>87.42463306317848</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.5681795455142</v>
+        <v>36.42480332296516</v>
       </c>
       <c r="C4" t="n">
-        <v>109.3382235696715</v>
+        <v>138.0160557584251</v>
       </c>
       <c r="D4" t="n">
-        <v>156.1774065392868</v>
+        <v>144.3336022352533</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.3076565509903</v>
+        <v>39.22082078466008</v>
       </c>
       <c r="C5" t="n">
-        <v>169.4741974456057</v>
+        <v>208.4004939189917</v>
       </c>
       <c r="D5" t="n">
-        <v>118.0797051282851</v>
+        <v>108.3113154710294</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.67304662341937</v>
+        <v>38.84284791852506</v>
       </c>
       <c r="C6" t="n">
-        <v>175.6179745787822</v>
+        <v>196.6695906009466</v>
       </c>
       <c r="D6" t="n">
-        <v>56.75483478250812</v>
+        <v>53.33344403320799</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.38625312059227</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>169.7785392339221</v>
+        <v>187.6247490017207</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>134.8528646553419</v>
+        <v>144.7832426837984</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>80.20780568926014</v>
+        <v>78.76561831172157</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>41.42484438069417</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2509,7 +2509,7 @@
         <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.559416264971435</v>
+        <v>2.394482650657971</v>
       </c>
       <c r="C2" t="n">
-        <v>1.992947839621025</v>
+        <v>5.789366211943441</v>
       </c>
       <c r="D2" t="n">
-        <v>11.29500733735955</v>
+        <v>11.89092819383737</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.11110172149591</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="C3" t="n">
-        <v>24.91675673378405</v>
+        <v>41.09105016125025</v>
       </c>
       <c r="D3" t="n">
-        <v>87.92041565382311</v>
+        <v>85.28442306792043</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.43528375254238</v>
+        <v>39.84521232456105</v>
       </c>
       <c r="C4" t="n">
-        <v>107.2323747440621</v>
+        <v>133.8171208273615</v>
       </c>
       <c r="D4" t="n">
-        <v>166.4641589843849</v>
+        <v>154.3268121167816</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.07480241863456</v>
+        <v>40.938879267092</v>
       </c>
       <c r="C5" t="n">
-        <v>203.8844544794564</v>
+        <v>251.8673735245193</v>
       </c>
       <c r="D5" t="n">
-        <v>124.5837836689203</v>
+        <v>111.0356653503143</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.97868895460962</v>
+        <v>31.51704654943536</v>
       </c>
       <c r="C6" t="n">
-        <v>208.7450873631823</v>
+        <v>230.4004782234585</v>
       </c>
       <c r="D6" t="n">
-        <v>55.2252718592916</v>
+        <v>51.96488773348793</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>176.1864064995411</v>
+        <v>191.7569250888955</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>98.71964040053801</v>
+        <v>99.13688317484291</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2806,7 +2806,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.204424506661589</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C2" t="n">
-        <v>4.357978059151591</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="D2" t="n">
-        <v>18.45587509213579</v>
+        <v>11.25770092459818</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.71639808665969</v>
+        <v>13.71501542832794</v>
       </c>
       <c r="C3" t="n">
-        <v>16.34119053718816</v>
+        <v>31.78899066351172</v>
       </c>
       <c r="D3" t="n">
-        <v>78.5790862479147</v>
+        <v>76.37997139040185</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.07868835172254</v>
+        <v>37.9818551819006</v>
       </c>
       <c r="C4" t="n">
-        <v>86.46742905153782</v>
+        <v>120.135484820978</v>
       </c>
       <c r="D4" t="n">
-        <v>170.9438737588631</v>
+        <v>159.980697145539</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.05779391249288</v>
+        <v>48.00746273766904</v>
       </c>
       <c r="C5" t="n">
-        <v>200.6446870554419</v>
+        <v>251.3519559797897</v>
       </c>
       <c r="D5" t="n">
-        <v>148.9311267342412</v>
+        <v>135.4566394934537</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.00764266411829</v>
+        <v>40.41266249761571</v>
       </c>
       <c r="C6" t="n">
-        <v>262.8030612021245</v>
+        <v>302.5716972057543</v>
       </c>
       <c r="D6" t="n">
-        <v>75.06933820523237</v>
+        <v>67.50202690089796</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>229.1860563133051</v>
+        <v>251.6435350479509</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>152.3770611761474</v>
+        <v>156.9667316935013</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>64.89843198923538</v>
+        <v>61.57030727183869</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.341468274628643</v>
+        <v>1.727875959474386</v>
       </c>
       <c r="C2" t="n">
-        <v>3.049308369390593</v>
+        <v>2.698824438974482</v>
       </c>
       <c r="D2" t="n">
-        <v>14.81260936167588</v>
+        <v>8.636434554259191</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.25850274585317</v>
+        <v>11.56498795602743</v>
       </c>
       <c r="C3" t="n">
-        <v>16.74861583445059</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="D3" t="n">
-        <v>75.96272861609695</v>
+        <v>70.09678608322227</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.76488893926206</v>
+        <v>34.3827680981318</v>
       </c>
       <c r="C4" t="n">
-        <v>69.8376046893011</v>
+        <v>105.9050518479204</v>
       </c>
       <c r="D4" t="n">
-        <v>171.5437216061579</v>
+        <v>161.4611726835432</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.05841580729864</v>
+        <v>52.35169632896118</v>
       </c>
       <c r="C5" t="n">
-        <v>190.3608798534566</v>
+        <v>248.946674104385</v>
       </c>
       <c r="D5" t="n">
-        <v>166.2344300215912</v>
+        <v>152.1218067730433</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.73596059194917</v>
+        <v>45.64537776125121</v>
       </c>
       <c r="C6" t="n">
-        <v>293.6358296016998</v>
+        <v>346.0434855498031</v>
       </c>
       <c r="D6" t="n">
-        <v>88.63414623481054</v>
+        <v>79.89953691012668</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="C7" t="n">
-        <v>282.8444588366188</v>
+        <v>311.5900316169654</v>
       </c>
       <c r="D7" t="n">
-        <v>44.79518424937346</v>
+        <v>44.25620475974196</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>193.0999559483051</v>
+        <v>198.5241120142688</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>73.1078062921472</v>
+        <v>65.67499442329461</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.048326621686346</v>
+        <v>2.329687302177681</v>
       </c>
       <c r="C2" t="n">
-        <v>10.15323475732051</v>
+        <v>6.32834570157494</v>
       </c>
       <c r="D2" t="n">
-        <v>21.72018620875643</v>
+        <v>10.41143440353742</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.7108674533327</v>
+        <v>8.948630324209677</v>
       </c>
       <c r="C3" t="n">
-        <v>14.40714755982194</v>
+        <v>19.1146278016854</v>
       </c>
       <c r="D3" t="n">
-        <v>71.59886007071988</v>
+        <v>62.70422587024377</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.83022406709009</v>
+        <v>28.66506946859837</v>
       </c>
       <c r="C4" t="n">
-        <v>57.52157973952487</v>
+        <v>88.36907435466389</v>
       </c>
       <c r="D4" t="n">
-        <v>168.1616007650277</v>
+        <v>159.3425611377786</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.24847395129502</v>
+        <v>51.78719139901926</v>
       </c>
       <c r="C5" t="n">
-        <v>164.3200219983099</v>
+        <v>226.8082633736194</v>
       </c>
       <c r="D5" t="n">
-        <v>183.1695779198487</v>
+        <v>167.2407214184442</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.51711296936016</v>
+        <v>54.17872880656449</v>
       </c>
       <c r="C6" t="n">
-        <v>298.1440150596011</v>
+        <v>365.4447836811285</v>
       </c>
       <c r="D6" t="n">
-        <v>110.4505437185832</v>
+        <v>97.61026549473914</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.73990327829938</v>
+        <v>27.008861091534</v>
       </c>
       <c r="C7" t="n">
-        <v>338.5390060985403</v>
+        <v>381.1782723893878</v>
       </c>
       <c r="D7" t="n">
-        <v>54.5567016726995</v>
+        <v>52.52055693409162</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>263.8643304704152</v>
+        <v>274.6291940474815</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>131.3499888465892</v>
+        <v>126.4687392610741</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>12.22766765639403</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.346017160251383</v>
+        <v>6.482480091141689</v>
       </c>
       <c r="C2" t="n">
-        <v>10.7275571643049</v>
+        <v>7.530986639277282</v>
       </c>
       <c r="D2" t="n">
-        <v>15.70010928631499</v>
+        <v>15.03644783824415</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.205987091442583</v>
+        <v>1.721985473248905</v>
       </c>
       <c r="C2" t="n">
-        <v>5.929756133650734</v>
+        <v>3.796418372322416</v>
       </c>
       <c r="D2" t="n">
-        <v>16.16054895960675</v>
+        <v>7.745989386507333</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.41205629834318</v>
+        <v>12.12458414744811</v>
       </c>
       <c r="C3" t="n">
-        <v>23.54721868635975</v>
+        <v>24.04300127700439</v>
       </c>
       <c r="D3" t="n">
-        <v>79.15831739342032</v>
+        <v>67.81422267084842</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.43979158043612</v>
+        <v>39.52614432068083</v>
       </c>
       <c r="C4" t="n">
-        <v>86.33980184998573</v>
+        <v>126.0956751334603</v>
       </c>
       <c r="D4" t="n">
-        <v>172.9859089836965</v>
+        <v>162.431139415339</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.86462629446773</v>
+        <v>30.50780990946964</v>
       </c>
       <c r="C5" t="n">
-        <v>248.4067128670492</v>
+        <v>322.7741014637451</v>
       </c>
       <c r="D5" t="n">
-        <v>165.5226629360123</v>
+        <v>148.5384276525424</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.68305972244431</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C6" t="n">
-        <v>278.501206993031</v>
+        <v>311.950333024424</v>
       </c>
       <c r="D6" t="n">
-        <v>84.28696740040567</v>
+        <v>77.28317927830892</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>185.5287176531537</v>
+        <v>193.1343171179537</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>96.80032363873549</v>
+        <v>93.2120357797134</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="D10" t="n">
         <v>18.93300447639974</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>9.980447161373073</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.65134069627214</v>
+        <v>6.770132168486005</v>
       </c>
       <c r="C2" t="n">
-        <v>5.885577486959628</v>
+        <v>9.645671194224912</v>
       </c>
       <c r="D2" t="n">
-        <v>21.98623983660732</v>
+        <v>18.88489883889164</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.47939597930871</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C3" t="n">
-        <v>27.03242303643592</v>
+        <v>18.97718312309085</v>
       </c>
       <c r="D3" t="n">
-        <v>16.32155558310322</v>
+        <v>15.76686813020378</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39637897872792</v>
+        <v>13.39701611772739</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13398406510501</v>
+        <v>70.13731967516107</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576044585732697</v>
+        <v>1.576119543262046</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.105488972710914</v>
+        <v>4.742823159216341</v>
       </c>
       <c r="C2" t="n">
-        <v>4.417864669110647</v>
+        <v>9.345256396725388</v>
       </c>
       <c r="D2" t="n">
-        <v>23.6846633649543</v>
+        <v>21.8222879699981</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.19316761802514</v>
+        <v>19.55641426859646</v>
       </c>
       <c r="C3" t="n">
-        <v>24.47987900539422</v>
+        <v>30.64034584954295</v>
       </c>
       <c r="D3" t="n">
-        <v>30.84651286743478</v>
+        <v>27.81782119983338</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.65985763044087</v>
+        <v>15.9916883544763</v>
       </c>
       <c r="C4" t="n">
-        <v>41.73409490753191</v>
+        <v>29.46912083837651</v>
       </c>
       <c r="D4" t="n">
-        <v>23.623795007291</v>
+        <v>23.3302524437212</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43515953387987</v>
+        <v>15.43719675102792</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11194266269824</v>
+        <v>86.12330818994522</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2495072702905</v>
+        <v>3.249936158111141</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.816454237034852</v>
+        <v>5.073672135547516</v>
       </c>
       <c r="C2" t="n">
-        <v>7.460300804571512</v>
+        <v>7.993389807977531</v>
       </c>
       <c r="D2" t="n">
-        <v>22.26603793231766</v>
+        <v>23.93599077724148</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.469439633546</v>
+        <v>17.78926840095221</v>
       </c>
       <c r="C3" t="n">
-        <v>20.11601046001715</v>
+        <v>34.03228416771568</v>
       </c>
       <c r="D3" t="n">
-        <v>42.63730279543898</v>
+        <v>38.81830422591889</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.47813649416398</v>
+        <v>28.44810322595982</v>
       </c>
       <c r="C4" t="n">
-        <v>53.06739040535709</v>
+        <v>56.5133248472634</v>
       </c>
       <c r="D4" t="n">
-        <v>33.75739481052658</v>
+        <v>32.02166486941822</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.59720570381833</v>
+        <v>13.84264262988003</v>
       </c>
       <c r="C5" t="n">
-        <v>45.52854978444584</v>
+        <v>33.37942194439156</v>
       </c>
       <c r="D5" t="n">
-        <v>31.14594591723007</v>
+        <v>31.02322745419922</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72184268601755</v>
+        <v>16.72524147816429</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0032403847071</v>
+        <v>102.0239730168021</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180460671504388</v>
+        <v>4.181310369541071</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.345436323174635</v>
+        <v>5.727516106575892</v>
       </c>
       <c r="C2" t="n">
-        <v>11.00342826919825</v>
+        <v>8.072911372021522</v>
       </c>
       <c r="D2" t="n">
-        <v>34.43578247416112</v>
+        <v>28.36661816650734</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.27523351455438</v>
+        <v>17.51928778228433</v>
       </c>
       <c r="C3" t="n">
-        <v>25.09838005906971</v>
+        <v>32.28477325415636</v>
       </c>
       <c r="D3" t="n">
-        <v>50.07404165510857</v>
+        <v>48.37561812676158</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.73186937021616</v>
+        <v>31.68983414538279</v>
       </c>
       <c r="C4" t="n">
-        <v>51.03811790067893</v>
+        <v>72.21147063816989</v>
       </c>
       <c r="D4" t="n">
-        <v>46.78813208899449</v>
+        <v>43.61021477034756</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.41530464109218</v>
+        <v>27.78346003018474</v>
       </c>
       <c r="C5" t="n">
-        <v>73.87651474457249</v>
+        <v>70.66129101316419</v>
       </c>
       <c r="D5" t="n">
-        <v>35.7356164345839</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.99499345048753</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="C6" t="n">
-        <v>43.31078172055229</v>
+        <v>33.32837106377072</v>
       </c>
       <c r="D6" t="n">
-        <v>38.52083467153211</v>
+        <v>38.48058301565798</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
         <v>39.88448223273092</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.40016181936776</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03821061817965</v>
+        <v>18.04147836233367</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6778502233625</v>
+        <v>117.6991683637958</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012736872726548</v>
+        <v>6.013826120777888</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.473063524726721</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C2" t="n">
-        <v>6.937029278207961</v>
+        <v>6.590472338608838</v>
       </c>
       <c r="D2" t="n">
-        <v>37.29365004122359</v>
+        <v>23.38130332434203</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.56623174563893</v>
+        <v>16.54244881655876</v>
       </c>
       <c r="C3" t="n">
-        <v>32.86400439966197</v>
+        <v>29.78622534684823</v>
       </c>
       <c r="D3" t="n">
-        <v>61.2512392679585</v>
+        <v>55.67000356931538</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.91282974296706</v>
+        <v>23.67484588791183</v>
       </c>
       <c r="C4" t="n">
-        <v>48.05164138436013</v>
+        <v>64.26029598147497</v>
       </c>
       <c r="D4" t="n">
-        <v>52.83766144256334</v>
+        <v>49.96604940764141</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.90555659840983</v>
+        <v>23.09561474240622</v>
       </c>
       <c r="C5" t="n">
-        <v>62.29189183446013</v>
+        <v>76.45360246822037</v>
       </c>
       <c r="D5" t="n">
-        <v>35.63744166415923</v>
+        <v>34.3366259560322</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.16229147083699</v>
+        <v>13.36354975020759</v>
       </c>
       <c r="C6" t="n">
-        <v>55.06426523579511</v>
+        <v>49.87180162803373</v>
       </c>
       <c r="D6" t="n">
-        <v>31.47679489356124</v>
+        <v>31.31578827006476</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>26.70942804173872</v>
+        <v>22.0382724649324</v>
       </c>
       <c r="D7" t="n">
         <v>31.32069700858599</v>
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>30.17499743772996</v>
@@ -5874,7 +5874,7 @@
         <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044935731043515</v>
+        <v>7.046308172913093</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04627247853296</v>
+        <v>66.05913912106024</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403084831902197</v>
+        <v>4.403942608070683</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.62639609303847</v>
+        <v>5.183627878423159</v>
       </c>
       <c r="C2" t="n">
-        <v>5.325981295538947</v>
+        <v>8.361545197070084</v>
       </c>
       <c r="D2" t="n">
-        <v>29.1019471969882</v>
+        <v>30.09547587368597</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.40977400776519</v>
+        <v>19.74785507092459</v>
       </c>
       <c r="C3" t="n">
-        <v>29.1922679857789</v>
+        <v>27.20913762320035</v>
       </c>
       <c r="D3" t="n">
-        <v>77.77896186895356</v>
+        <v>61.85992284459152</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.71085175779947</v>
+        <v>29.13729011434109</v>
       </c>
       <c r="C4" t="n">
-        <v>69.30157044278235</v>
+        <v>70.76928326063133</v>
       </c>
       <c r="D4" t="n">
-        <v>72.68369128391261</v>
+        <v>67.55307778151878</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.88225669541517</v>
+        <v>30.48326621686347</v>
       </c>
       <c r="C5" t="n">
-        <v>78.3189231062893</v>
+        <v>102.0035864712436</v>
       </c>
       <c r="D5" t="n">
-        <v>46.8784528777852</v>
+        <v>44.8167826988669</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.82898027747859</v>
+        <v>23.30570875111504</v>
       </c>
       <c r="C6" t="n">
-        <v>80.62406671586082</v>
+        <v>91.29075552250242</v>
       </c>
       <c r="D6" t="n">
-        <v>36.18623863083319</v>
+        <v>35.66296710446964</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.37845589222053</v>
+        <v>11.49822911213864</v>
       </c>
       <c r="C7" t="n">
-        <v>56.95216607106171</v>
+        <v>50.42452558552467</v>
       </c>
       <c r="D7" t="n">
         <v>33.83593462686632</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>28.12216298814988</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6185,7 +6185,7 @@
         <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.260637701015464</v>
+        <v>7.263001591851909</v>
       </c>
       <c r="C21" t="n">
-        <v>75.32911614803545</v>
+        <v>75.35364151546356</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445478275761599</v>
+        <v>5.447251193888932</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.245477983790708</v>
+        <v>4.498367980858886</v>
       </c>
       <c r="C2" t="n">
-        <v>7.347399818583129</v>
+        <v>8.561821728736433</v>
       </c>
       <c r="D2" t="n">
-        <v>27.13452479767759</v>
+        <v>30.85436684906876</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.17138924208247</v>
+        <v>18.6973850273805</v>
       </c>
       <c r="C3" t="n">
-        <v>24.19026343264141</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="D3" t="n">
-        <v>82.59443435828416</v>
+        <v>70.97054154000192</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.93455136564751</v>
+        <v>34.395530818287</v>
       </c>
       <c r="C4" t="n">
-        <v>71.45847014901258</v>
+        <v>69.27604500247193</v>
       </c>
       <c r="D4" t="n">
-        <v>93.39758609581605</v>
+        <v>81.86008707550754</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.84070449666732</v>
+        <v>37.42913122440965</v>
       </c>
       <c r="C5" t="n">
-        <v>104.9488295839841</v>
+        <v>116.901607883189</v>
       </c>
       <c r="D5" t="n">
-        <v>62.39006660488482</v>
+        <v>58.95394964002097</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>33.04660947265189</v>
       </c>
       <c r="C6" t="n">
-        <v>104.4932986492135</v>
+        <v>129.6505835705381</v>
       </c>
       <c r="D6" t="n">
-        <v>42.34474197957343</v>
+        <v>41.33845058272045</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="C7" t="n">
-        <v>88.99150239915636</v>
+        <v>93.90220441579891</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00992495469625</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>52.90638378186061</v>
+        <v>46.89808783187013</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>29.95312245657017</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
         <v>32.28280975874785</v>
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
@@ -6566,7 +6566,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.462521057157896</v>
+        <v>7.465119342386531</v>
       </c>
       <c r="C21" t="n">
-        <v>83.95336189302633</v>
+        <v>83.98259260184848</v>
       </c>
       <c r="D21" t="n">
-        <v>6.529705925013158</v>
+        <v>6.531979424588214</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_23_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497633542676</v>
+        <v>10.84497647636464</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907195310061</v>
+        <v>37.7890724441954</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.352488483553611</v>
+        <v>1.269399781591126</v>
       </c>
       <c r="C2" t="n">
-        <v>13.90351098754333</v>
+        <v>2.575124228239384</v>
       </c>
       <c r="D2" t="n">
-        <v>28.36956340962008</v>
+        <v>16.95478285234242</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8369731278328</v>
+        <v>9.468956607460486</v>
       </c>
       <c r="C3" t="n">
-        <v>31.76444697090555</v>
+        <v>26.41392198276044</v>
       </c>
       <c r="D3" t="n">
-        <v>78.07839491874883</v>
+        <v>69.37029278207962</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.21234490822035</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="C4" t="n">
-        <v>71.89240263428968</v>
+        <v>88.05000635078369</v>
       </c>
       <c r="D4" t="n">
-        <v>97.11153766098174</v>
+        <v>75.86160860255953</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.05592822807562</v>
+        <v>16.3460992757094</v>
       </c>
       <c r="C5" t="n">
-        <v>122.4484824121835</v>
+        <v>113.9318210778424</v>
       </c>
       <c r="D5" t="n">
-        <v>72.64933011426398</v>
+        <v>50.06913291658734</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.861722109084</v>
+        <v>11.43147026824986</v>
       </c>
       <c r="C6" t="n">
-        <v>156.2166764474567</v>
+        <v>71.84920573530283</v>
       </c>
       <c r="D6" t="n">
-        <v>49.79129831628549</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.10489244010094</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>140.3742137440259</v>
+        <v>37.90822410408209</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.10418842983718</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>84.19959185472769</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.651707142888808</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.7769491075268</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.651707142888808</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.939573610693203</v>
+        <v>1.448077863764045</v>
       </c>
       <c r="C2" t="n">
-        <v>17.50456156672063</v>
+        <v>10.51648140789183</v>
       </c>
       <c r="D2" t="n">
-        <v>35.61682496237003</v>
+        <v>13.2359225486555</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.17076734727672</v>
+        <v>6.710245558526949</v>
       </c>
       <c r="C3" t="n">
-        <v>42.54894550205677</v>
+        <v>16.6209886328985</v>
       </c>
       <c r="D3" t="n">
-        <v>81.11690406339271</v>
+        <v>67.50497214401069</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.51490312757761</v>
+        <v>17.45940117232528</v>
       </c>
       <c r="C4" t="n">
-        <v>75.31281163588557</v>
+        <v>76.27001564752621</v>
       </c>
       <c r="D4" t="n">
-        <v>109.491376211534</v>
+        <v>92.60629744619312</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.56567627075797</v>
+        <v>20.39580855572749</v>
       </c>
       <c r="C5" t="n">
-        <v>125.6882498361979</v>
+        <v>141.8870869562703</v>
       </c>
       <c r="D5" t="n">
-        <v>87.96459430051422</v>
+        <v>65.08987279156354</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.42903341341842</v>
+        <v>16.78494049950772</v>
       </c>
       <c r="C6" t="n">
-        <v>174.0079083438175</v>
+        <v>128.4430338943145</v>
       </c>
       <c r="D6" t="n">
-        <v>58.6064109527176</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.14777054391831</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>177.6835717485175</v>
+        <v>72.40291144049802</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>31.62013005838127</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.44766125760332</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>130.0128484734051</v>
+        <v>39.72151211382594</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>69.66874408417063</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.82184300934863</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7062287453636</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.799573385517208</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.701810739816227</v>
+        <v>0.7579092276785376</v>
       </c>
       <c r="C2" t="n">
-        <v>11.32249627307846</v>
+        <v>4.329507375728434</v>
       </c>
       <c r="D2" t="n">
-        <v>30.80626121156066</v>
+        <v>8.93488585635022</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.91198686398306</v>
+        <v>6.597344572538566</v>
       </c>
       <c r="C3" t="n">
-        <v>53.38744015694155</v>
+        <v>29.86476516318797</v>
       </c>
       <c r="D3" t="n">
-        <v>87.55716900325179</v>
+        <v>65.49729808882596</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.25139383221197</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="C4" t="n">
-        <v>87.59054842519618</v>
+        <v>69.40367220402401</v>
       </c>
       <c r="D4" t="n">
-        <v>120.7608581085832</v>
+        <v>103.7864403021558</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.64559874542947</v>
+        <v>20.83759502263855</v>
       </c>
       <c r="C5" t="n">
-        <v>130.7687942056752</v>
+        <v>160.6875554925967</v>
       </c>
       <c r="D5" t="n">
-        <v>100.899120303966</v>
+        <v>74.7846313710008</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.82275530055039</v>
+        <v>13.44405306195583</v>
       </c>
       <c r="C6" t="n">
-        <v>183.1450342272425</v>
+        <v>165.072040739763</v>
       </c>
       <c r="D6" t="n">
-        <v>69.35360307110744</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.05280305851362</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>206.8483507985775</v>
+        <v>70.06733365209486</v>
       </c>
       <c r="D7" t="n">
-        <v>48.98724694650735</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.70768553050848</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>173.739891220558</v>
+        <v>40.05530633326986</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>105.2796785603152</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>56.22959976073607</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.49392657288993</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.974561715896357</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6565831646008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.968202144870446</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.023423076181681</v>
+        <v>0.7745989386507334</v>
       </c>
       <c r="C2" t="n">
-        <v>7.970809610779853</v>
+        <v>3.041454387756618</v>
       </c>
       <c r="D2" t="n">
-        <v>25.48518865454295</v>
+        <v>9.020297906619694</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.55427084673872</v>
+        <v>4.481678269886689</v>
       </c>
       <c r="C3" t="n">
-        <v>71.23561342014857</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="D3" t="n">
-        <v>94.12015240614171</v>
+        <v>57.71694753266999</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.36854060418683</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C4" t="n">
-        <v>111.5206487162122</v>
+        <v>73.05381016841365</v>
       </c>
       <c r="D4" t="n">
-        <v>115.5919564457237</v>
+        <v>113.7541247433737</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.87596529856219</v>
+        <v>25.08365384350601</v>
       </c>
       <c r="C5" t="n">
-        <v>109.4403253309132</v>
+        <v>145.0286796098601</v>
       </c>
       <c r="D5" t="n">
-        <v>67.59332943739291</v>
+        <v>92.87333282174828</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.57867567062465</v>
+        <v>20.12582793705961</v>
       </c>
       <c r="C6" t="n">
-        <v>136.2116034780195</v>
+        <v>213.8167960033214</v>
       </c>
       <c r="D6" t="n">
-        <v>32.24157635516951</v>
+        <v>51.11960296013142</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>122.1686843164731</v>
+        <v>150.4950508271063</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>77.60715602071035</v>
+        <v>64.50573290753667</v>
       </c>
       <c r="D8" t="n">
-        <v>26.53664044579129</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>24.00864010735575</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.367795536194059</v>
+        <v>0.3995713156284518</v>
       </c>
       <c r="C2" t="n">
-        <v>4.34619708670063</v>
+        <v>1.563924092865169</v>
       </c>
       <c r="D2" t="n">
-        <v>18.15055155611503</v>
+        <v>7.16577649329747</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.15942834318226</v>
+        <v>3.711006322052944</v>
       </c>
       <c r="C3" t="n">
-        <v>52.54804586981053</v>
+        <v>17.33275571847744</v>
       </c>
       <c r="D3" t="n">
-        <v>93.1089522707675</v>
+        <v>52.67567307136261</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.60500293219007</v>
+        <v>13.55400880483146</v>
       </c>
       <c r="C4" t="n">
-        <v>144.9462128027033</v>
+        <v>66.76178913189584</v>
       </c>
       <c r="D4" t="n">
-        <v>132.8854422560313</v>
+        <v>116.957567502331</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>26.45810062945155</v>
       </c>
       <c r="C5" t="n">
-        <v>153.7416904850505</v>
+        <v>145.6422719250143</v>
       </c>
       <c r="D5" t="n">
-        <v>84.65119579868124</v>
+        <v>108.7285582453343</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.56988099901544</v>
+        <v>24.67426505083509</v>
       </c>
       <c r="C6" t="n">
-        <v>158.672027455778</v>
+        <v>231.3262663085632</v>
       </c>
       <c r="D6" t="n">
-        <v>39.56737772425921</v>
+        <v>62.67182819600364</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>10.06095047312131</v>
       </c>
       <c r="C7" t="n">
-        <v>151.3933499764921</v>
+        <v>211.6392795953019</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>40.54323494228053</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>102.3913768144211</v>
+        <v>102.0575825949772</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>46.92655851529327</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.889684404225862</v>
+        <v>1.278235510929347</v>
       </c>
       <c r="C2" t="n">
-        <v>11.80257090045516</v>
+        <v>6.746570223584081</v>
       </c>
       <c r="D2" t="n">
-        <v>16.82421040767759</v>
+        <v>15.24163310843173</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.19807635654638</v>
+        <v>2.518182861393069</v>
       </c>
       <c r="C3" t="n">
-        <v>34.24335992412875</v>
+        <v>11.4029995848267</v>
       </c>
       <c r="D3" t="n">
-        <v>87.42463306317848</v>
+        <v>46.84409170813656</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.42480332296516</v>
+        <v>10.49095596758142</v>
       </c>
       <c r="C4" t="n">
-        <v>138.0160557584251</v>
+        <v>54.7393067456894</v>
       </c>
       <c r="D4" t="n">
-        <v>144.3336022352533</v>
+        <v>116.6640249387612</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.22082078466008</v>
+        <v>24.29825568010856</v>
       </c>
       <c r="C5" t="n">
-        <v>208.4004939189917</v>
+        <v>134.4748917892069</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3113154710294</v>
+        <v>123.2584242681871</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.84284791852506</v>
+        <v>29.7057220351</v>
       </c>
       <c r="C6" t="n">
-        <v>196.6695906009466</v>
+        <v>234.7074054019893</v>
       </c>
       <c r="D6" t="n">
-        <v>53.33344403320799</v>
+        <v>78.49072895453251</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>187.6247490017207</v>
+        <v>270.7473636248896</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>47.31042186765379</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>144.7832426837984</v>
+        <v>179.4978415059656</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>78.76561831172157</v>
+        <v>82.98124295375739</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.15820991576653</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.394482650657971</v>
+        <v>0.8482300164692441</v>
       </c>
       <c r="C2" t="n">
-        <v>5.789366211943441</v>
+        <v>3.453788423540279</v>
       </c>
       <c r="D2" t="n">
-        <v>11.89092819383737</v>
+        <v>10.97397583807085</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.59921025695582</v>
+        <v>4.113522880794135</v>
       </c>
       <c r="C3" t="n">
-        <v>41.09105016125025</v>
+        <v>18.68756755033803</v>
       </c>
       <c r="D3" t="n">
-        <v>85.28442306792043</v>
+        <v>52.76893910326606</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.84521232456105</v>
+        <v>16.80850244440964</v>
       </c>
       <c r="C4" t="n">
-        <v>133.8171208273615</v>
+        <v>75.12137083355744</v>
       </c>
       <c r="D4" t="n">
-        <v>154.3268121167816</v>
+        <v>121.7180621202238</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.938879267092</v>
+        <v>18.53048791765855</v>
       </c>
       <c r="C5" t="n">
-        <v>251.8673735245193</v>
+        <v>199.2947839621026</v>
       </c>
       <c r="D5" t="n">
-        <v>111.0356653503143</v>
+        <v>113.6127530739622</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.51704654943536</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="C6" t="n">
-        <v>230.4004782234585</v>
+        <v>238.1287961512894</v>
       </c>
       <c r="D6" t="n">
-        <v>51.96488773348793</v>
+        <v>66.45548384817086</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.26435217434965</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>191.7569250888955</v>
+        <v>126.1810871837298</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>99.13688317484291</v>
+        <v>61.16779071309751</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
         <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>35.47545329295849</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.390555659840983</v>
+        <v>0.4162610266006476</v>
       </c>
       <c r="C2" t="n">
-        <v>4.249985811684442</v>
+        <v>1.673879835740812</v>
       </c>
       <c r="D2" t="n">
-        <v>11.25770092459818</v>
+        <v>8.265333922053896</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.71501542832794</v>
+        <v>3.529382996767284</v>
       </c>
       <c r="C3" t="n">
-        <v>31.78899066351172</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="D3" t="n">
-        <v>76.37997139040185</v>
+        <v>49.28373475318988</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.9818551819006</v>
+        <v>11.61407534123977</v>
       </c>
       <c r="C4" t="n">
-        <v>120.135484820978</v>
+        <v>58.18524118759571</v>
       </c>
       <c r="D4" t="n">
-        <v>159.980697145539</v>
+        <v>115.7706345278966</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.00746273766904</v>
+        <v>17.40147805777472</v>
       </c>
       <c r="C5" t="n">
-        <v>251.3519559797897</v>
+        <v>153.668059407232</v>
       </c>
       <c r="D5" t="n">
-        <v>135.4566394934537</v>
+        <v>116.9261515757951</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.41266249761571</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>302.5716972057543</v>
+        <v>227.5828623122702</v>
       </c>
       <c r="D6" t="n">
-        <v>67.50202690089796</v>
+        <v>71.12467592956868</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>251.6435350479509</v>
+        <v>164.3887443376071</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>156.9667316935013</v>
+        <v>69.01195487002953</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>61.57030727183869</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.727875959474386</v>
+        <v>0.2405281875404685</v>
       </c>
       <c r="C2" t="n">
-        <v>2.698824438974482</v>
+        <v>5.145339717957533</v>
       </c>
       <c r="D2" t="n">
-        <v>8.636434554259191</v>
+        <v>9.307949983964008</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.56498795602743</v>
+        <v>2.375829444277281</v>
       </c>
       <c r="C3" t="n">
-        <v>25.75124228239384</v>
+        <v>10.234719816773</v>
       </c>
       <c r="D3" t="n">
-        <v>70.09678608322227</v>
+        <v>44.45844478681681</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.3827680981318</v>
+        <v>9.087056750508477</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9050518479204</v>
+        <v>47.28587817504762</v>
       </c>
       <c r="D4" t="n">
-        <v>161.4611726835432</v>
+        <v>114.6219897139279</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.35169632896118</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="C5" t="n">
-        <v>248.946674104385</v>
+        <v>129.0752794158494</v>
       </c>
       <c r="D5" t="n">
-        <v>152.1218067730433</v>
+        <v>132.6341148437441</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.64537776125121</v>
+        <v>17.34846368174539</v>
       </c>
       <c r="C6" t="n">
-        <v>346.0434855498031</v>
+        <v>237.6860279366741</v>
       </c>
       <c r="D6" t="n">
-        <v>79.89953691012668</v>
+        <v>90.96874227550947</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.09142570968197</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>311.5900316169654</v>
+        <v>254.6977521558627</v>
       </c>
       <c r="D7" t="n">
-        <v>44.25620475974196</v>
+        <v>47.19064864773568</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>198.5241120142688</v>
+        <v>146.4522137810179</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>58.68593251676156</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.329687302177681</v>
+        <v>0.1767145867644259</v>
       </c>
       <c r="C2" t="n">
-        <v>6.32834570157494</v>
+        <v>16.34708102341364</v>
       </c>
       <c r="D2" t="n">
-        <v>10.41143440353742</v>
+        <v>11.93412509282423</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.948630324209677</v>
+        <v>1.546252634188726</v>
       </c>
       <c r="C3" t="n">
-        <v>19.1146278016854</v>
+        <v>15.83559046950105</v>
       </c>
       <c r="D3" t="n">
-        <v>62.70422587024377</v>
+        <v>42.06788912697583</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.66506946859837</v>
+        <v>6.777004402415732</v>
       </c>
       <c r="C4" t="n">
-        <v>88.36907435466389</v>
+        <v>35.12300586713388</v>
       </c>
       <c r="D4" t="n">
-        <v>159.3425611377786</v>
+        <v>110.1933258200705</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.78719139901926</v>
+        <v>16.00248757922301</v>
       </c>
       <c r="C5" t="n">
-        <v>226.8082633736194</v>
+        <v>106.96141237769</v>
       </c>
       <c r="D5" t="n">
-        <v>167.2407214184442</v>
+        <v>143.7524075943392</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.17872880656449</v>
+        <v>21.01136436629024</v>
       </c>
       <c r="C6" t="n">
-        <v>365.4447836811285</v>
+        <v>222.4306503603829</v>
       </c>
       <c r="D6" t="n">
-        <v>97.61026549473914</v>
+        <v>110.3700404068349</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.008861091534</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>381.1782723893878</v>
+        <v>302.0680606334756</v>
       </c>
       <c r="D7" t="n">
-        <v>52.52055693409162</v>
+        <v>60.06626978893259</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>274.6291940474815</v>
+        <v>242.3346033162827</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>126.4687392610741</v>
+        <v>118.5921774299019</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>25.84843530511426</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>45.55309347705201</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.22766765639403</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.482480091141689</v>
+        <v>4.193044444838127</v>
       </c>
       <c r="C2" t="n">
-        <v>7.530986639277282</v>
+        <v>6.788785374866693</v>
       </c>
       <c r="D2" t="n">
-        <v>15.03644783824415</v>
+        <v>18.61884521104076</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.721985473248905</v>
+        <v>0.5586144437164351</v>
       </c>
       <c r="C2" t="n">
-        <v>3.796418372322416</v>
+        <v>14.63589477491145</v>
       </c>
       <c r="D2" t="n">
-        <v>7.745989386507333</v>
+        <v>13.57855249743763</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.12458414744811</v>
+        <v>1.065196259107789</v>
       </c>
       <c r="C3" t="n">
-        <v>24.04300127700439</v>
+        <v>40.44309667644735</v>
       </c>
       <c r="D3" t="n">
-        <v>67.81422267084842</v>
+        <v>41.631011398586</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.52614432068083</v>
+        <v>4.862596379134452</v>
       </c>
       <c r="C4" t="n">
-        <v>126.0956751334603</v>
+        <v>36.89702396870788</v>
       </c>
       <c r="D4" t="n">
-        <v>162.431139415339</v>
+        <v>106.7091032176986</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.50780990946964</v>
+        <v>13.59720570381833</v>
       </c>
       <c r="C5" t="n">
-        <v>322.7741014637451</v>
+        <v>86.56560382196251</v>
       </c>
       <c r="D5" t="n">
-        <v>148.5384276525424</v>
+        <v>148.4647965747239</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.7446888436336</v>
+        <v>21.41388092503143</v>
       </c>
       <c r="C6" t="n">
-        <v>311.950333024424</v>
+        <v>199.527458168009</v>
       </c>
       <c r="D6" t="n">
-        <v>77.28317927830892</v>
+        <v>128.1210206473215</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>193.1343171179537</v>
+        <v>311.4103717870882</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>74.73848922890117</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>93.2120357797134</v>
+        <v>317.4383026911636</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72343455150543</v>
+        <v>200.2421704967006</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>87.12029127486197</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.770132168486005</v>
+        <v>4.728096943652639</v>
       </c>
       <c r="C2" t="n">
-        <v>9.645671194224912</v>
+        <v>9.801769079200154</v>
       </c>
       <c r="D2" t="n">
-        <v>18.88489883889164</v>
+        <v>18.26050729899067</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76901155206151</v>
+        <v>6.764241682260523</v>
       </c>
       <c r="C3" t="n">
-        <v>18.97718312309085</v>
+        <v>13.40085616296896</v>
       </c>
       <c r="D3" t="n">
-        <v>15.76686813020378</v>
+        <v>15.66869335977909</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39701611772739</v>
+        <v>11.67736476110942</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13731967516107</v>
+        <v>59.94380577369503</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576119543262046</v>
+        <v>0.7784909840739613</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.742823159216341</v>
+        <v>2.66544501703009</v>
       </c>
       <c r="C2" t="n">
-        <v>9.345256396725388</v>
+        <v>6.238024912784233</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8222879699981</v>
+        <v>17.18058482431918</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.55641426859646</v>
+        <v>12.86089492563322</v>
       </c>
       <c r="C3" t="n">
-        <v>30.64034584954295</v>
+        <v>29.98257488769759</v>
       </c>
       <c r="D3" t="n">
-        <v>27.81782119983338</v>
+        <v>27.79818624574844</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.9916883544763</v>
+        <v>8.461683462903258</v>
       </c>
       <c r="C4" t="n">
-        <v>29.46912083837651</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D4" t="n">
-        <v>23.3302524437212</v>
+        <v>22.59001467471911</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.080544369477244</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.84656962069702</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43719675102792</v>
+        <v>13.6277604467877</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12330818994522</v>
+        <v>73.75023300614519</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249936158111141</v>
+        <v>1.6032659349162</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.073672135547516</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C2" t="n">
-        <v>7.993389807977531</v>
+        <v>5.094288837336698</v>
       </c>
       <c r="D2" t="n">
-        <v>23.93599077724148</v>
+        <v>14.97656122828509</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.78926840095221</v>
+        <v>10.79922474671491</v>
       </c>
       <c r="C3" t="n">
-        <v>34.03228416771568</v>
+        <v>26.40410450571797</v>
       </c>
       <c r="D3" t="n">
-        <v>38.81830422591889</v>
+        <v>35.50981446260713</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.44810322595982</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="C4" t="n">
-        <v>56.5133248472634</v>
+        <v>54.96903570848316</v>
       </c>
       <c r="D4" t="n">
-        <v>32.02166486941822</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.84264262988003</v>
+        <v>8.099418560036186</v>
       </c>
       <c r="C5" t="n">
-        <v>33.37942194439156</v>
+        <v>26.80171232593793</v>
       </c>
       <c r="D5" t="n">
-        <v>31.02322745419922</v>
+        <v>28.07798434145878</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.427682146153116</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72524147816429</v>
+        <v>14.83811938129067</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0239730168021</v>
+        <v>87.3800363564895</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181310369541071</v>
+        <v>2.473019896881778</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.727516106575892</v>
+        <v>1.446114368355552</v>
       </c>
       <c r="C2" t="n">
-        <v>8.072911372021522</v>
+        <v>5.979825266567322</v>
       </c>
       <c r="D2" t="n">
-        <v>28.36661816650734</v>
+        <v>25.01002276568749</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.51928778228433</v>
+        <v>7.770533079113505</v>
       </c>
       <c r="C3" t="n">
-        <v>32.28477325415636</v>
+        <v>22.36421270274234</v>
       </c>
       <c r="D3" t="n">
-        <v>48.37561812676158</v>
+        <v>39.25027321578748</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68983414538279</v>
+        <v>20.11404696460865</v>
       </c>
       <c r="C4" t="n">
-        <v>72.21147063816989</v>
+        <v>61.69498923027806</v>
       </c>
       <c r="D4" t="n">
-        <v>43.61021477034756</v>
+        <v>42.23184099358505</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.78346003018474</v>
+        <v>18.50594422505238</v>
       </c>
       <c r="C5" t="n">
-        <v>70.66129101316419</v>
+        <v>70.17041716104079</v>
       </c>
       <c r="D5" t="n">
-        <v>35.04839304161113</v>
+        <v>33.60031517784709</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.19625172985813</v>
+        <v>7.889324551327369</v>
       </c>
       <c r="C6" t="n">
-        <v>33.32837106377072</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04147836233367</v>
+        <v>16.08190120277118</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6991683637958</v>
+        <v>101.5699023332917</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013826120777888</v>
+        <v>3.385663411109723</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.243915399009714</v>
+        <v>2.502474898125119</v>
       </c>
       <c r="C2" t="n">
-        <v>6.590472338608838</v>
+        <v>4.257839793318416</v>
       </c>
       <c r="D2" t="n">
-        <v>23.38130332434203</v>
+        <v>23.7602579381813</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.54244881655876</v>
+        <v>6.224280444924778</v>
       </c>
       <c r="C3" t="n">
-        <v>29.78622534684823</v>
+        <v>22.84036033930204</v>
       </c>
       <c r="D3" t="n">
-        <v>55.67000356931538</v>
+        <v>49.52426294073035</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.67484588791183</v>
+        <v>17.51045205294611</v>
       </c>
       <c r="C4" t="n">
-        <v>64.26029598147497</v>
+        <v>57.90446134418112</v>
       </c>
       <c r="D4" t="n">
-        <v>49.96604940764141</v>
+        <v>51.85493199061228</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.09561474240622</v>
+        <v>24.39643045053324</v>
       </c>
       <c r="C5" t="n">
-        <v>76.45360246822037</v>
+        <v>94.29686699290615</v>
       </c>
       <c r="D5" t="n">
-        <v>34.3366259560322</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.36354975020759</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="C6" t="n">
-        <v>49.87180162803373</v>
+        <v>72.17121898229578</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>37.19253002768617</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>22.0382724649324</v>
+        <v>29.88341836956866</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.046308172913093</v>
+        <v>17.35154376446416</v>
       </c>
       <c r="C21" t="n">
-        <v>66.05913912106024</v>
+        <v>115.3877660336867</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403942608070683</v>
+        <v>4.337885941116039</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.183627878423159</v>
+        <v>2.723368131580652</v>
       </c>
       <c r="C2" t="n">
-        <v>8.361545197070084</v>
+        <v>8.305585577928015</v>
       </c>
       <c r="D2" t="n">
-        <v>30.09547587368597</v>
+        <v>31.71535958569321</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.74785507092459</v>
+        <v>7.372925258893545</v>
       </c>
       <c r="C3" t="n">
-        <v>27.20913762320035</v>
+        <v>19.3306122966197</v>
       </c>
       <c r="D3" t="n">
-        <v>61.85992284459152</v>
+        <v>56.09215508214151</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.13729011434109</v>
+        <v>14.56226369709294</v>
       </c>
       <c r="C4" t="n">
-        <v>70.76928326063133</v>
+        <v>57.44500341859361</v>
       </c>
       <c r="D4" t="n">
-        <v>67.55307778151878</v>
+        <v>63.5583463729385</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.48326621686347</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="C5" t="n">
-        <v>102.0035864712436</v>
+        <v>99.77011044408214</v>
       </c>
       <c r="D5" t="n">
-        <v>44.8167826988669</v>
+        <v>48.52288028239862</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.30570875111504</v>
+        <v>24.31200014796801</v>
       </c>
       <c r="C6" t="n">
-        <v>91.29075552250242</v>
+        <v>110.9738152449467</v>
       </c>
       <c r="D6" t="n">
-        <v>35.66296710446964</v>
+        <v>41.41895389446869</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>50.42452558552467</v>
+        <v>66.29447722467437</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>25.03456645829366</v>
+        <v>32.29459073119883</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.263001591851909</v>
+        <v>18.64249893143501</v>
       </c>
       <c r="C21" t="n">
-        <v>75.35364151546356</v>
+        <v>128.722016431337</v>
       </c>
       <c r="D21" t="n">
-        <v>5.447251193888932</v>
+        <v>5.326428266124289</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.498367980858886</v>
+        <v>2.417062847855647</v>
       </c>
       <c r="C2" t="n">
-        <v>8.561821728736433</v>
+        <v>5.115887286830128</v>
       </c>
       <c r="D2" t="n">
-        <v>30.85436684906876</v>
+        <v>24.82643594499334</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6973850273805</v>
+        <v>9.856746950637977</v>
       </c>
       <c r="C3" t="n">
-        <v>30.29182541453534</v>
+        <v>33.40887437551896</v>
       </c>
       <c r="D3" t="n">
-        <v>70.97054154000192</v>
+        <v>63.38163178617408</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.395530818287</v>
+        <v>12.30326222962103</v>
       </c>
       <c r="C4" t="n">
-        <v>69.27604500247193</v>
+        <v>86.19941192827845</v>
       </c>
       <c r="D4" t="n">
-        <v>81.86008707550754</v>
+        <v>60.02307288994574</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.42913122440965</v>
+        <v>13.69538047424301</v>
       </c>
       <c r="C5" t="n">
-        <v>116.901607883189</v>
+        <v>66.29251372926588</v>
       </c>
       <c r="D5" t="n">
-        <v>58.95394964002097</v>
+        <v>39.17173339944774</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.04660947265189</v>
+        <v>8.45284773356504</v>
       </c>
       <c r="C6" t="n">
-        <v>129.6505835705381</v>
+        <v>43.63279496754524</v>
       </c>
       <c r="D6" t="n">
-        <v>41.33845058272045</v>
+        <v>25.55980148006571</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.8823545064064</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>93.90220441579891</v>
+        <v>22.69702517448201</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>46.89808783187013</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.06718511671205</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.465119342386531</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.98259260184848</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.531979424588214</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
